--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/KANSAS_2012.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/KANSAS_2012.xlsx
@@ -3228,7 +3228,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C160">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C193">
@@ -10464,7 +10464,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C562">
@@ -11166,7 +11166,7 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C601">
@@ -11292,7 +11292,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C608">
@@ -11310,7 +11310,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C609">
@@ -16152,7 +16152,7 @@
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C878">
